--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="M2" t="n">
         <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>7.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>12</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="M32" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M33" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N34" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AI39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2760,27 +2760,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>45994.60416666666</v>
+        <v>45994.625</v>
       </c>
     </row>
     <row r="21">
@@ -2998,27 +2998,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>45994.625</v>
+        <v>45994.6875</v>
       </c>
     </row>
     <row r="23">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>7.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>45994.6875</v>
+        <v>45994.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.25</v>
+        <v>5.2</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.2</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4277,7 +4277,7 @@
         <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>45994.69791666666</v>
+        <v>45994.71875</v>
       </c>
     </row>
     <row r="33">
@@ -4426,27 +4426,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>45994.71875</v>
+        <v>45994.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>45994.79166666666</v>
+        <v>45994.8125</v>
       </c>
     </row>
     <row r="37">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>45994.8125</v>
+        <v>45994.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="AI38" s="3" t="n">
-        <v>45994.83333333334</v>
+        <v>45994.89583333334</v>
       </c>
     </row>
     <row r="39">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5131,125 +5131,6 @@
         <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>45994.89583333334</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" s="3" t="n">
         <v>45994.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="N23" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>12</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="M29" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="N29" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>19</v>
+        <v>2.35</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>7.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>7.1</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>1.25</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="N22" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>7.1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.25</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.2</v>
+        <v>1.11</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N30" t="n">
-        <v>1.6</v>
+        <v>19</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.35</v>
+        <v>12</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>7.1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>9</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>19</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="N31" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M33" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>7.1</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="M29" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="N29" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>19</v>
+        <v>3.39</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N31" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N30" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="O14" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M30" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>2.35</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1971,70 +1971,70 @@
         <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N25" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>9.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.07</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>7.8</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>17</v>
+        <v>2.28</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N31" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1971,70 +1971,70 @@
         <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.85</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>2.33</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>17</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>3.39</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>4.9</v>
       </c>
       <c r="N30" t="n">
-        <v>2.28</v>
+        <v>9.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2447,70 +2447,70 @@
         <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>9.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N30" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>3.85</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N31" t="n">
-        <v>3.39</v>
+        <v>9.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1971,70 +1971,70 @@
         <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.92</v>
+        <v>3.85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2447,70 +2447,70 @@
         <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N31" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M33" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.44</v>
+        <v>12</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>12</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.85</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N30" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="M31" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>17</v>
+        <v>3.39</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>7.8</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="N31" t="n">
-        <v>3.39</v>
+        <v>17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M33" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>10.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2685,70 +2685,70 @@
         <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.35</v>
+        <v>2.83</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>9.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>2.28</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.07</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>7.8</v>
+        <v>3.72</v>
       </c>
       <c r="N31" t="n">
-        <v>17</v>
+        <v>1.57</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>2.85</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.92</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="O19" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.60416666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.6875</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>7.8</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M33" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>11</v>
+        <v>2.36</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.36</v>
+        <v>11</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,16 +5101,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2566,70 +2566,70 @@
         <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.6875</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>9.1</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N30" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M32" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2.33</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N25" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>3.39</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3.39</v>
+        <v>9.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M30" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.07</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>7.8</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>17</v>
+        <v>2.28</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="N38" t="n">
-        <v>2.36</v>
+        <v>11</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>11</v>
+        <v>2.36</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,16 +5101,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N11" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z15" t="n">
         <v>2.33</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>3.39</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>9.1</v>
+        <v>3.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.07</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>7.8</v>
+        <v>3.72</v>
       </c>
       <c r="N30" t="n">
-        <v>17</v>
+        <v>1.57</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>1.24</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>4.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.28</v>
+        <v>9.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>2.33</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,16 +2846,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M31" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N31" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M38" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>4.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.36</v>
+        <v>11</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5101,16 +5101,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,76 +778,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.33</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>45994.4375</v>
+        <v>45994.375</v>
       </c>
     </row>
     <row r="4">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>45994.54166666666</v>
+        <v>45994.4375</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>45994.54166666666</v>
+        <v>45994.5</v>
       </c>
     </row>
     <row r="6">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,76 +1254,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>45994.54166666666</v>
+        <v>45994.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>45994.54166666666</v>
+        <v>45994.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>45994.54166666666</v>
+        <v>45994.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>3.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="O10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>1.96</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>45994.5625</v>
+        <v>45994.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>3.69</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>45994.58333333334</v>
+        <v>45994.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.5</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.27</v>
+        <v>4.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,16 +1888,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>45994.58333333334</v>
+        <v>45994.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,10 +2602,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>45994.60416666666</v>
+        <v>45994.625</v>
       </c>
     </row>
     <row r="19">
@@ -2641,27 +2641,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,22 +2721,22 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>45994.60416666666</v>
+        <v>45994.625</v>
       </c>
     </row>
     <row r="20">
@@ -2760,27 +2760,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>5.1</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>45994.625</v>
+        <v>45994.6875</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>45994.625</v>
+        <v>45994.6875</v>
       </c>
     </row>
     <row r="22">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,56 +3396,56 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2.3</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>45994.6875</v>
+        <v>45994.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>5.7</v>
+        <v>3.72</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
         <v>2.2</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>45994.6875</v>
+        <v>45994.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>3.39</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,56 +3991,56 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.95</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>45994.69791666666</v>
+        <v>45994.71875</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>45994.69791666666</v>
+        <v>45994.71875</v>
       </c>
     </row>
     <row r="32">
@@ -4188,27 +4188,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>45994.71875</v>
+        <v>45994.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4307,27 +4307,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>45994.71875</v>
+        <v>45994.79166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>45994.79166666666</v>
+        <v>45994.8125</v>
       </c>
     </row>
     <row r="35">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="AI35" s="3" t="n">
-        <v>45994.79166666666</v>
+        <v>45994.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>45994.8125</v>
+        <v>45994.89583333334</v>
       </c>
     </row>
     <row r="37">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.09</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4893,244 +4893,6 @@
         <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>45994.83333333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Atlético Mineiro</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="3" t="n">
-        <v>45994.89583333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45994</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Flamengo</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ceará</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>11</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="3" t="n">
         <v>45994.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>8.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2123,37 +2123,37 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>3.85</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2361,37 +2361,37 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2447,70 +2447,70 @@
         <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>9.1</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>3.39</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,16 +2727,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>17</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>3.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.57</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45994.33333333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45994.4375</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>8.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.96</v>
+        <v>2.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2123,37 +2123,37 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2480,37 +2480,37 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -787,19 +787,19 @@
         <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>7.17</v>
+        <v>8.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
         <v>3.08</v>
@@ -808,37 +808,37 @@
         <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>6.85</v>
+        <v>8.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
         <v>1.17</v>
@@ -1025,61 +1025,61 @@
         <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>6.64</v>
+        <v>6.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
         <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
         <v>4.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
         <v>1.08</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>10.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,16 +1537,16 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.87</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8.5</v>
+        <v>1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T14" t="n">
         <v>3.8</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.96</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>5.5</v>
+        <v>1.44</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2480,37 +2480,37 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.04</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1144,40 +1144,40 @@
         <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA6" t="n">
         <v>1.85</v>
@@ -1186,22 +1186,22 @@
         <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45994.54166666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>1.44</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>2.33</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.6</v>
+        <v>3.85</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AC12" t="n">
-        <v>4.25</v>
+        <v>6.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.87</v>
+        <v>3.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>1.92</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.44</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2480,37 +2480,37 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2572,40 +2572,40 @@
         <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="AA18" t="n">
         <v>1.6</v>
@@ -2620,16 +2620,16 @@
         <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.04</v>
+        <v>7.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH21" t="n">
         <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AH23" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N26" t="n">
-        <v>3.39</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N27" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1299,10 +1299,10 @@
         <v>3.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
         <v>3.14</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
-        <v>10.08</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>10.08</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="O12" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.32</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.96</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.09</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2242,37 +2242,37 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2480,37 +2480,37 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>1.74</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.85</v>
       </c>
-      <c r="Q18" t="n">
-        <v>9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.88</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.79</v>
+        <v>12</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.74</v>
+        <v>5.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>4.88</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>3.16</v>
       </c>
       <c r="M20" t="n">
-        <v>3.96</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.04</v>
+        <v>2.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>2.09</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>3.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>3.31</v>
       </c>
       <c r="O21" t="n">
-        <v>1.73</v>
+        <v>2.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.5</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
         <v>6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="N22" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.7</v>
       </c>
-      <c r="O22" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="AB22" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AC22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.05</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>3.72</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>4.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>1.71</v>
       </c>
       <c r="O23" t="n">
-        <v>2.79</v>
+        <v>4.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.28</v>
+        <v>2.37</v>
       </c>
       <c r="R23" t="n">
         <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
         <v>2.7</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W23" t="n">
         <v>1.08</v>
@@ -3197,34 +3197,34 @@
         <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>1.92</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.75</v>
+        <v>6.04</v>
       </c>
       <c r="R24" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.02</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.39</v>
+        <v>9.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M26" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.07</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>7.8</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>3.39</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>8.1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AF30" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>4.4</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>1.81</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.35</v>
+        <v>2.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4744,16 +4744,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4863,16 +4863,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O3" t="n">
         <v>8.15</v>
@@ -817,19 +817,19 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AA3" t="n">
         <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AD3" t="n">
         <v>1.19</v>
@@ -838,7 +838,7 @@
         <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG3" t="n">
         <v>1.17</v>
@@ -1019,19 +1019,19 @@
         <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
-        <v>6.53</v>
+        <v>6.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
         <v>1.48</v>
@@ -1067,13 +1067,13 @@
         <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
         <v>1.56</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.15</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1766,37 +1766,37 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>4.61</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>6.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
         <v>1.24</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,34 +2206,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>1.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2242,37 +2242,37 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.16</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>3.31</v>
       </c>
       <c r="O20" t="n">
-        <v>3.65</v>
+        <v>2.79</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.46</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.05</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>3.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="N21" t="n">
-        <v>3.31</v>
+        <v>6.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.79</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>6.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.46</v>
       </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>3.16</v>
       </c>
       <c r="M22" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>9.25</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.73</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.6</v>
+        <v>2.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.72</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>9.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.04</v>
+        <v>8.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>9.1</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>17</v>
+        <v>3.39</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,16 +3560,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3.39</v>
+        <v>9.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>4.4</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>8.1</v>
+        <v>1.81</v>
       </c>
       <c r="O30" t="n">
-        <v>1.8</v>
+        <v>3.79</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH30" t="n">
         <v>1.24</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>3.1</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.4</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.81</v>
+        <v>8.1</v>
       </c>
       <c r="O31" t="n">
-        <v>3.79</v>
+        <v>1.8</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.68</v>
+        <v>2.32</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="V31" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.24</v>
+        <v>3.1</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
-        <v>6.52</v>
+        <v>6.15</v>
       </c>
       <c r="P2" t="n">
         <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
@@ -683,7 +683,7 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
@@ -701,31 +701,31 @@
         <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45994.33333333334</v>
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>8.15</v>
+        <v>7.7</v>
       </c>
       <c r="P3" t="n">
         <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
@@ -817,10 +817,10 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AA3" t="n">
         <v>2.12</v>
@@ -829,7 +829,7 @@
         <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD3" t="n">
         <v>1.19</v>
@@ -838,13 +838,13 @@
         <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45994.375</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>5.42</v>
+        <v>4.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
         <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>3.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>45994.4375</v>
@@ -1019,25 +1019,25 @@
         <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
         <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="T5" t="n">
         <v>3.25</v>
@@ -1052,10 +1052,10 @@
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
         <v>2.63</v>
@@ -1064,10 +1064,10 @@
         <v>2.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="AD5" t="n">
         <v>1.15</v>
@@ -1076,7 +1076,7 @@
         <v>2.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
         <v>1.23</v>
@@ -1144,40 +1144,40 @@
         <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
         <v>7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="AA6" t="n">
         <v>1.85</v>
@@ -1186,10 +1186,10 @@
         <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
         <v>2.05</v>
@@ -1198,10 +1198,10 @@
         <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>45994.54166666666</v>
@@ -1299,7 +1299,7 @@
         <v>3.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB7" t="n">
         <v>2.07</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>10.08</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="U11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.27</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AC11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AE11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH11" t="n">
-        <v>2.09</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,70 +1849,70 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="O12" t="n">
-        <v>4.61</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.92</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.35</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
         <v>1.24</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
         <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4.1</v>
+        <v>2.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>6.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2682,31 +2682,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>1.53</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10.51</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
         <v>1.68</v>
@@ -2721,34 +2721,34 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
         <v>5.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
         <v>1.02</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>3.31</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.79</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2929,13 +2929,13 @@
         <v>6.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="P21" t="n">
         <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.04</v>
+        <v>6.29</v>
       </c>
       <c r="R21" t="n">
         <v>1.25</v>
@@ -2944,13 +2944,13 @@
         <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
         <v>1.15</v>
@@ -2959,10 +2959,10 @@
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" t="n">
         <v>1.63</v>
@@ -2977,10 +2977,10 @@
         <v>1.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
         <v>1.19</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.16</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.65</v>
+        <v>2.79</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.46</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.05</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.09</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.95</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.92</v>
+        <v>5.7</v>
       </c>
       <c r="N23" t="n">
-        <v>1.71</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>4.18</v>
+        <v>1.68</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.37</v>
+        <v>8.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.7</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>9.25</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.73</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.6</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.72</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N26" t="n">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.64</v>
+        <v>2.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.24</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
-        <v>3.79</v>
+        <v>4.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R30" t="n">
         <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
         <v>6.9</v>
@@ -4039,7 +4039,7 @@
         <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
         <v>3</v>
@@ -4048,16 +4048,16 @@
         <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG30" t="n">
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4110,34 +4110,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="P31" t="n">
         <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
         <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="U31" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V31" t="n">
         <v>4.8</v>
@@ -4155,28 +4155,28 @@
         <v>4.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4476,40 +4476,40 @@
         <v>2.03</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA34" t="n">
         <v>1.96</v>
@@ -4518,22 +4518,22 @@
         <v>1.74</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4595,40 +4595,40 @@
         <v>3.09</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
         <v>2.3</v>
@@ -4637,22 +4637,22 @@
         <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45994.83333333334</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>3.52</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>2.33</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.33</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.33</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>2.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>6.41</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>2.09</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
         <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>1.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2123,37 +2123,37 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8.5</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.45</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2563,43 +2563,43 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
         <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
         <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.22</v>
@@ -2611,16 +2611,16 @@
         <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
         <v>2.1</v>
@@ -2629,7 +2629,7 @@
         <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.6</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.7</v>
       </c>
-      <c r="O20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.29</v>
+        <v>8.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH21" t="n">
         <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.3</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.28</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.68</v>
+        <v>3.65</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M25" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O25" t="n">
-        <v>5.05</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.23</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>5.8</v>
+        <v>3.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>6.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.51</v>
+        <v>1.64</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.15</v>
+        <v>6.1</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.07</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>7.8</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>4.22</v>
       </c>
       <c r="R27" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>4.35</v>
+        <v>2.69</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>2.94</v>
       </c>
       <c r="U27" t="n">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>3.42</v>
+        <v>7.7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.24</v>
       </c>
-      <c r="AB27" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AE27" t="n">
-        <v>2.13</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>1.8</v>
+        <v>5.05</v>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.43</v>
+        <v>2.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U28" t="n">
         <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH29" t="n">
         <v>3.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V29" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>4.85</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.41</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V30" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>3.24</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
-        <v>1.77</v>
+        <v>4.85</v>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>2.41</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="U31" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>12</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC36" t="n">
         <v>3.55</v>
       </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="AD36" t="n">
         <v>1.32</v>
       </c>
-      <c r="V36" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH36" t="n">
         <v>3.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>3.05</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S37" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>6.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.52</v>
+        <v>2.89</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.49</v>
+        <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.8</v>
+        <v>1.38</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1614,70 +1614,70 @@
         <v>2.88</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1885,37 +1885,37 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.45</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2123,37 +2123,37 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>1.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>10.51</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>5.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>4.72</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.51</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.72</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.93</v>
+        <v>2.79</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.29</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N21" t="n">
-        <v>9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="Z21" t="n">
         <v>3.3</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N22" t="n">
+        <v>9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.7</v>
       </c>
-      <c r="O22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.65</v>
+        <v>1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>6.29</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.48</v>
+        <v>2.52</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>2.79</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.88</v>
+        <v>3.48</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N25" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>8.43</v>
       </c>
       <c r="R25" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>4.35</v>
+        <v>3.04</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>3.42</v>
+        <v>5.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.64</v>
+        <v>2.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M26" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O26" t="n">
-        <v>3.24</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.04</v>
+        <v>11</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="S26" t="n">
-        <v>2.99</v>
+        <v>4.35</v>
       </c>
       <c r="T26" t="n">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="V26" t="n">
-        <v>5.75</v>
+        <v>3.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.62</v>
+        <v>6.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.02</v>
+        <v>3.38</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.72</v>
+        <v>1.64</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.59</v>
+        <v>2.13</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.45</v>
+        <v>6.1</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>3.39</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.22</v>
+        <v>3.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="T27" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.38</v>
+        <v>2.72</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O28" t="n">
-        <v>5.05</v>
+        <v>2.7</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>4.22</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.44</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.51</v>
+        <v>3.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
-        <v>1.8</v>
+        <v>5.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.43</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
         <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>4.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>2.41</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="U30" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>4.85</v>
+        <v>1.77</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.41</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V31" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>3.24</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4357,40 +4357,40 @@
         <v>2.84</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA33" t="n">
         <v>1.96</v>
@@ -4399,22 +4399,22 @@
         <v>1.74</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O2" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
         <v>2.15</v>
@@ -683,7 +683,7 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
@@ -692,7 +692,7 @@
         <v>7.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
         <v>1.07</v>
@@ -704,28 +704,28 @@
         <v>2.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE2" t="n">
         <v>2.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45994.33333333334</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
         <v>4.9</v>
@@ -924,7 +924,7 @@
         <v>3.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
         <v>7.3</v>
@@ -936,16 +936,16 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z4" t="n">
         <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
         <v>3.67</v>
@@ -954,10 +954,10 @@
         <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG4" t="n">
         <v>1.28</v>
@@ -1138,10 +1138,10 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.92</v>
@@ -1150,13 +1150,13 @@
         <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
         <v>2.81</v>
@@ -1165,7 +1165,7 @@
         <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="W6" t="n">
         <v>1.06</v>
@@ -1174,16 +1174,16 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
         <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
         <v>3.18</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>2.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.41</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.09</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2361,37 +2361,37 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.3</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.28</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.6</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="N21" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>3.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.5</v>
+        <v>2.75</v>
       </c>
       <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.33</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.29</v>
+        <v>8.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH23" t="n">
         <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>2.6</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>4.9</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>9.1</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
-        <v>1.8</v>
+        <v>3.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.43</v>
+        <v>3.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U25" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M26" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N26" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>8.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>4.35</v>
+        <v>3.04</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>3.42</v>
+        <v>5.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.64</v>
+        <v>2.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.12</v>
+        <v>1.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>3.24</v>
+        <v>5.05</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.04</v>
+        <v>2.18</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="V27" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.72</v>
+        <v>2.51</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>7.8</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="O29" t="n">
-        <v>5.05</v>
+        <v>1.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>3.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>11</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>4.35</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>5.8</v>
+        <v>3.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>6.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.51</v>
+        <v>1.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.42</v>
+        <v>2.12</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>1.62</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.15</v>
+        <v>6.1</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>4.85</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.41</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V30" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>3.24</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
-        <v>1.77</v>
+        <v>4.85</v>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>2.41</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="U31" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
         <v>6.1</v>
@@ -704,10 +704,10 @@
         <v>2.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.34</v>
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
         <v>3.08</v>
@@ -808,7 +808,7 @@
         <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
@@ -817,22 +817,22 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>2.4</v>
@@ -844,7 +844,7 @@
         <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45994.375</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
         <v>4.9</v>
@@ -942,10 +942,10 @@
         <v>2.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
         <v>3.67</v>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>5.6</v>
+        <v>6.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
         <v>2.43</v>
@@ -1046,22 +1046,22 @@
         <v>1.27</v>
       </c>
       <c r="V5" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
         <v>2.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
         <v>1.55</v>
@@ -1073,7 +1073,7 @@
         <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AF5" t="n">
         <v>1.53</v>
@@ -1082,7 +1082,7 @@
         <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45994.5</v>
@@ -1138,10 +1138,10 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="N6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>1.92</v>
@@ -1180,10 +1180,10 @@
         <v>3.28</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
         <v>3.18</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.83</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>1.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>6.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.88</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4.1</v>
+        <v>2.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>6.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2209,70 +2209,70 @@
         <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.27</v>
+        <v>6.33</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.09</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>4.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.79</v>
+        <v>2.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.51</v>
+        <v>2.49</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="T18" t="n">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>6.15</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.72</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.75</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>5.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>4.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2822,7 +2822,7 @@
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="T20" t="n">
         <v>2.75</v>
@@ -2834,7 +2834,7 @@
         <v>7.7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.06</v>
@@ -2843,7 +2843,7 @@
         <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA20" t="n">
         <v>1.97</v>
@@ -2858,7 +2858,7 @@
         <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AF20" t="n">
         <v>1.91</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.29</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.25</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.65</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.48</v>
+        <v>2.52</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
         <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3170,16 +3170,16 @@
         <v>1.68</v>
       </c>
       <c r="P23" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="R23" t="n">
         <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
         <v>2.3</v>
@@ -3188,7 +3188,7 @@
         <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="W23" t="n">
         <v>1.11</v>
@@ -3224,7 +3224,7 @@
         <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3334,10 +3334,10 @@
         <v>1.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
         <v>1.3</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>1.07</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>7.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>17</v>
       </c>
       <c r="O25" t="n">
-        <v>3.24</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.04</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>4.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.56</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>5.75</v>
+        <v>3.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.62</v>
+        <v>6.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>3.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.72</v>
+        <v>1.64</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.21</v>
+        <v>1.63</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.45</v>
+        <v>6.05</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4.9</v>
+        <v>3.72</v>
       </c>
       <c r="N26" t="n">
-        <v>9.1</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>5.05</v>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.43</v>
+        <v>2.18</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S26" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U26" t="n">
         <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.92</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.72</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>5.05</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.18</v>
+        <v>3.02</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3762,10 +3762,10 @@
         <v>3.39</v>
       </c>
       <c r="O28" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q28" t="n">
         <v>4.22</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="P29" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>11</v>
+        <v>8.43</v>
       </c>
       <c r="R29" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>3.42</v>
+        <v>5.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.95</v>
+        <v>3.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.64</v>
+        <v>2.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.12</v>
+        <v>1.45</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -4018,7 +4018,7 @@
         <v>2.39</v>
       </c>
       <c r="U30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V30" t="n">
         <v>4.8</v>
@@ -4057,7 +4057,7 @@
         <v>1.04</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4119,16 +4119,16 @@
         <v>1.78</v>
       </c>
       <c r="O31" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
         <v>3.12</v>
@@ -4170,7 +4170,7 @@
         <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>1.25</v>
@@ -4482,22 +4482,22 @@
         <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.77</v>
+        <v>2.97</v>
       </c>
       <c r="T34" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U34" t="n">
         <v>1.4</v>
       </c>
       <c r="V34" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="W34" t="n">
         <v>1.04</v>
@@ -4509,7 +4509,7 @@
         <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AA34" t="n">
         <v>1.96</v>
@@ -4521,7 +4521,7 @@
         <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
         <v>1.82</v>
@@ -4533,7 +4533,7 @@
         <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4595,19 +4595,19 @@
         <v>3.09</v>
       </c>
       <c r="O35" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P35" t="n">
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="T35" t="n">
         <v>3.25</v>
@@ -4616,7 +4616,7 @@
         <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
@@ -4625,7 +4625,7 @@
         <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z35" t="n">
         <v>2.8</v>
@@ -4646,7 +4646,7 @@
         <v>1.95</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
         <v>1.38</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.7</v>
+        <v>3.55</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>3.08</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="V36" t="n">
-        <v>6.25</v>
+        <v>8.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
         <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.52</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.49</v>
+        <v>1.84</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>3.55</v>
+        <v>1.68</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="R37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.44</v>
       </c>
-      <c r="S37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V37" t="n">
-        <v>8.300000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.89</v>
+        <v>3.54</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.84</v>
+        <v>2.49</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.38</v>
+        <v>4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,43 +659,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
-        <v>6.1</v>
+        <v>6.68</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.38</v>
@@ -704,28 +704,28 @@
         <v>2.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>45994.33333333334</v>
@@ -781,10 +781,10 @@
         <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="O3" t="n">
         <v>7.9</v>
@@ -820,19 +820,19 @@
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
         <v>2.4</v>
@@ -897,70 +897,70 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="O4" t="n">
         <v>4.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="U4" t="n">
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.67</v>
+        <v>3.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
         <v>1.15</v>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O5" t="n">
         <v>5.6</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6.26</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
         <v>2.43</v>
@@ -1055,13 +1055,13 @@
         <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z5" t="n">
         <v>2.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB5" t="n">
         <v>1.55</v>
@@ -1073,16 +1073,16 @@
         <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45994.5</v>
@@ -1138,67 +1138,67 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
         <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.75</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
         <v>2.79</v>
@@ -1299,7 +1299,7 @@
         <v>3.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
         <v>2.07</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>1.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.13</v>
+        <v>6.29</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
         <v>2.13</v>
       </c>
       <c r="T10" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.74</v>
+        <v>3.19</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.55</v>
+        <v>6.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1733,70 +1733,70 @@
         <v>2.88</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.83</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.78</v>
-      </c>
       <c r="Q12" t="n">
-        <v>6.24</v>
+        <v>3.38</v>
       </c>
       <c r="R12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.05</v>
+        <v>6.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="U13" t="n">
         <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
         <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>3.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -2123,37 +2123,37 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>5.37</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>6.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>5.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="O16" t="n">
-        <v>6.33</v>
+        <v>2.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>6.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.16</v>
       </c>
-      <c r="T16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2447,10 +2447,10 @@
         <v>2.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2566,31 +2566,31 @@
         <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="T18" t="n">
         <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V18" t="n">
         <v>6.15</v>
@@ -2614,22 +2614,22 @@
         <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
         <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
         <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
         <v>3.4</v>
       </c>
       <c r="N21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF21" t="n">
         <v>2.25</v>
       </c>
-      <c r="O21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>5.7</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>8.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.39</v>
+        <v>8.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.79</v>
+        <v>1.97</v>
       </c>
       <c r="P24" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.28</v>
+        <v>6.32</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>17</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.36</v>
       </c>
-      <c r="P25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>11</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V25" t="n">
-        <v>3.42</v>
+        <v>7.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.95</v>
+        <v>3.18</v>
       </c>
       <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.24</v>
       </c>
-      <c r="AB25" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AE25" t="n">
-        <v>2.11</v>
+        <v>1.78</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>6.05</v>
+        <v>1.71</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3518,70 +3518,70 @@
         <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.72</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
         <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
         <v>5.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
         <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.92</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3637,67 +3637,67 @@
         <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
         <v>1.44</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.39</v>
+        <v>8.58</v>
       </c>
       <c r="O28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.71</v>
       </c>
-      <c r="P28" t="n">
+      <c r="AD28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE28" t="n">
         <v>2.03</v>
       </c>
-      <c r="Q28" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>21</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.24</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.71</v>
+        <v>1.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.2</v>
+        <v>7.71</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>4.3</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>1.81</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="T30" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.75</v>
+        <v>3.64</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5.32</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>7.83</v>
       </c>
       <c r="O31" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="V31" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>3.24</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>3.55</v>
+        <v>1.68</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.08</v>
+        <v>10.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="S36" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U36" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
-        <v>8.4</v>
+        <v>6.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>2.49</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.36</v>
+        <v>4</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.68</v>
+        <v>3.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.5</v>
+        <v>3.08</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="T37" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>6.25</v>
+        <v>8.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
         <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.54</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.49</v>
+        <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>4</v>
+        <v>1.36</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="O9" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.83</v>
+        <v>3.39</v>
       </c>
       <c r="M10" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>2.65</v>
+        <v>4.44</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.29</v>
+        <v>3.28</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.19</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
         <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.88</v>
+        <v>5.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>6.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>5.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M12" t="n">
         <v>3.25</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
         <v>2.69</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1.49</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>7.5</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>5.03</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE13" t="n">
-        <v>3.08</v>
+        <v>2.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.39</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.37</v>
+        <v>2.88</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>6.33</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.69</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.64</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>2.37</v>
       </c>
       <c r="O16" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41</v>
+        <v>3.38</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE16" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>1.18</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>13</v>
       </c>
       <c r="O18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V18" t="n">
         <v>4.5</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.15</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>5.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.92</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>4</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.22</v>
       </c>
-      <c r="S19" t="n">
+      <c r="Z19" t="n">
         <v>3.9</v>
       </c>
-      <c r="T19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.72</v>
-      </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.72</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.26</v>
       </c>
-      <c r="M22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N22" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AH22" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.88</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>1.97</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.28</v>
+        <v>6.32</v>
       </c>
       <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.4</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.2</v>
+        <v>2.62</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>8.92</v>
       </c>
       <c r="O24" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="P24" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.32</v>
+        <v>8.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD24" t="n">
         <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>1.09</v>
       </c>
       <c r="M25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>21</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P25" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.6</v>
-      </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.18</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.79</v>
+        <v>3.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.38</v>
+        <v>1.71</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.71</v>
+        <v>7.71</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.15</v>
+        <v>4.28</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AH26" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>8.58</v>
       </c>
       <c r="O27" t="n">
-        <v>2.99</v>
+        <v>1.79</v>
       </c>
       <c r="P27" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.24</v>
+        <v>8.43</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
         <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
         <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.6</v>
+        <v>4.23</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.54</v>
+        <v>2.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.42</v>
+        <v>1.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,40 +3753,40 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O28" t="n">
         <v>5</v>
       </c>
-      <c r="N28" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.79</v>
-      </c>
       <c r="P28" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.43</v>
+        <v>2.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U28" t="n">
         <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
@@ -3795,31 +3795,31 @@
         <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB28" t="n">
         <v>2.18</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="AD28" t="n">
         <v>1.45</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.03</v>
+        <v>1.71</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.09</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>21</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>2.99</v>
       </c>
       <c r="P29" t="n">
-        <v>3.77</v>
+        <v>2.37</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.29</v>
+        <v>3.24</v>
       </c>
       <c r="R29" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="U29" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.53</v>
+        <v>2.16</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.71</v>
+        <v>2.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>7.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.3</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5.32</v>
       </c>
       <c r="N30" t="n">
-        <v>1.81</v>
+        <v>7.83</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="V30" t="n">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.64</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>3.24</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.33</v>
       </c>
-      <c r="M31" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="N31" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4467,31 +4467,31 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="R34" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U34" t="n">
         <v>1.4</v>
@@ -4506,34 +4506,34 @@
         <v>1.06</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z34" t="n">
         <v>3.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AC34" t="n">
         <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.09</v>
+        <v>3.03</v>
       </c>
       <c r="O35" t="n">
         <v>3.25</v>
@@ -4601,43 +4601,43 @@
         <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.87</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="T35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U35" t="n">
         <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD35" t="n">
         <v>1.16</v>
@@ -4649,10 +4649,10 @@
         <v>1.76</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45994.83333333334</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>1.68</v>
+        <v>3.55</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>10.5</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="T36" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V36" t="n">
-        <v>6.25</v>
+        <v>8.4</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
         <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.54</v>
+        <v>2.85</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF36" t="n">
         <v>1.9</v>
       </c>
-      <c r="AC36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AG36" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>4</v>
+        <v>1.39</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.22</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="O37" t="n">
-        <v>3.55</v>
+        <v>1.69</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.08</v>
+        <v>10.7</v>
       </c>
       <c r="R37" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="T37" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>8.4</v>
+        <v>6.25</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
         <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>3.62</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>4.21</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>4.44</v>
+        <v>6.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.28</v>
+        <v>2.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.37</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA11" t="n">
         <v>3</v>
       </c>
-      <c r="N11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.64</v>
+        <v>6.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.14</v>
+        <v>1.92</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.88</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="N12" t="n">
-        <v>5.5</v>
+        <v>2.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.41</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>4.61</v>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.03</v>
+        <v>3.24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.29</v>
+        <v>6.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.06</v>
+        <v>2.69</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.19</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>5.34</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="M16" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>4.56</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.38</v>
+        <v>3.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
         <v>3.92</v>
@@ -2361,13 +2361,13 @@
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y16" t="n">
         <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AA16" t="n">
         <v>2.88</v>
@@ -2388,10 +2388,10 @@
         <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2444,31 +2444,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S17" t="n">
         <v>2.13</v>
       </c>
       <c r="T17" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="U17" t="n">
         <v>1.18</v>
@@ -2483,10 +2483,10 @@
         <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
         <v>2.9</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.18</v>
+        <v>3.96</v>
       </c>
       <c r="M18" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>13</v>
+        <v>1.82</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>4.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>2.47</v>
       </c>
       <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.22</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z18" t="n">
-        <v>5.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>1.18</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V19" t="n">
         <v>4.5</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.15</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>5.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.69</v>
+        <v>2.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.17</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.92</v>
+        <v>1.08</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>4.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2801,25 +2801,25 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
         <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
         <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
         <v>2.7</v>
@@ -2828,13 +2828,13 @@
         <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V20" t="n">
         <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
         <v>1.06</v>
@@ -2843,7 +2843,7 @@
         <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="AA20" t="n">
         <v>2.09</v>
@@ -2858,7 +2858,7 @@
         <v>1.27</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
         <v>2</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.81</v>
+        <v>1.97</v>
       </c>
       <c r="P21" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.32</v>
+        <v>6.32</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.71</v>
+        <v>2.62</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.88</v>
+        <v>2.14</v>
       </c>
       <c r="M22" t="n">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="P22" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AG22" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>4.25</v>
+        <v>5.75</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>9.35</v>
       </c>
       <c r="O23" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.32</v>
+        <v>8.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
         <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>4.88</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>8.92</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.68</v>
+        <v>4.18</v>
       </c>
       <c r="P24" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.5</v>
+        <v>2.29</v>
       </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>21</v>
+        <v>8.58</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="P25" t="n">
-        <v>3.77</v>
+        <v>2.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>13.29</v>
+        <v>8.43</v>
       </c>
       <c r="R25" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="V25" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>4.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.53</v>
+        <v>2.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.71</v>
+        <v>2.71</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.71</v>
+        <v>3.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
         <v>2.18</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AC26" t="n">
-        <v>3.38</v>
+        <v>2.66</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="N27" t="n">
-        <v>8.58</v>
+        <v>21</v>
       </c>
       <c r="O27" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>2.62</v>
+        <v>3.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.43</v>
+        <v>13.29</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="V27" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.23</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.18</v>
+        <v>3.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.71</v>
+        <v>1.71</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.25</v>
+        <v>7.71</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.15</v>
+        <v>3.24</v>
       </c>
       <c r="R28" t="n">
         <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U28" t="n">
         <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA28" t="n">
         <v>1.68</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="P29" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.24</v>
+        <v>4.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="T29" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE29" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3991,25 +3991,25 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>5.32</v>
+        <v>5.4</v>
       </c>
       <c r="N30" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="P30" t="n">
         <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
         <v>3.5</v>
@@ -4024,7 +4024,7 @@
         <v>4.8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
@@ -4036,16 +4036,16 @@
         <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE30" t="n">
         <v>1.83</v>
@@ -4054,10 +4054,10 @@
         <v>1.87</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4110,31 +4110,31 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="O31" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
         <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U31" t="n">
         <v>1.44</v>
@@ -4152,10 +4152,10 @@
         <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AB31" t="n">
         <v>1.95</v>
@@ -4170,7 +4170,7 @@
         <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="AG31" t="n">
         <v>1.25</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,28 +4229,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="M32" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="O32" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
         <v>2.85</v>
@@ -4259,13 +4259,13 @@
         <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
         <v>1.27</v>
@@ -4274,28 +4274,28 @@
         <v>3.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.88</v>
+        <v>1.22</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>13</v>
       </c>
       <c r="O36" t="n">
-        <v>3.55</v>
+        <v>1.69</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>10.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U36" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
-        <v>8.4</v>
+        <v>6.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
         <v>1.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.85</v>
+        <v>3.62</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.39</v>
+        <v>4.21</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>13</v>
+        <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>1.69</v>
+        <v>3.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>10.7</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.35</v>
       </c>
-      <c r="S37" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V37" t="n">
-        <v>6.25</v>
+        <v>8.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X37" t="n">
         <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.62</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.21</v>
+        <v>1.39</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
         <v>3.08</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="O8" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="O10" t="n">
-        <v>6.33</v>
+        <v>7.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="T10" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
@@ -1650,34 +1650,34 @@
         <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AD10" t="n">
         <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.6</v>
+        <v>5.34</v>
       </c>
       <c r="R11" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="T11" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="O12" t="n">
         <v>4.1</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>4.61</v>
+        <v>6.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.24</v>
+        <v>2.47</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
         <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.27</v>
+        <v>4.61</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.41</v>
+        <v>3.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z14" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH14" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.34</v>
+        <v>5.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S15" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>5.5</v>
       </c>
       <c r="O17" t="n">
-        <v>7.6</v>
+        <v>2.27</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>6.41</v>
       </c>
       <c r="R17" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE17" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M19" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="N19" t="n">
         <v>13</v>
@@ -2697,43 +2697,43 @@
         <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
         <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="V19" t="n">
         <v>4.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z19" t="n">
         <v>5.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
         <v>1.71</v>
@@ -2745,10 +2745,10 @@
         <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.2</v>
+        <v>4.78</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.28</v>
+        <v>2.14</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>2.37</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.46</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.37</v>
-      </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>3.28</v>
       </c>
       <c r="M21" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>6.5</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.97</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.32</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.65</v>
+        <v>3.27</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.85</v>
+        <v>3.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.14</v>
+        <v>4.88</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.78</v>
+        <v>4.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.32</v>
+        <v>2.29</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.26</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.88</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.65</v>
       </c>
-      <c r="N24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="AA24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.4</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>2.62</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="N25" t="n">
-        <v>8.58</v>
+        <v>21</v>
       </c>
       <c r="O25" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>2.62</v>
+        <v>3.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.43</v>
+        <v>13.29</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.23</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.18</v>
+        <v>3.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.71</v>
+        <v>1.71</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.25</v>
+        <v>7.71</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,40 +3515,40 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>1.66</v>
+        <v>8.58</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>1.79</v>
       </c>
       <c r="P26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.48</v>
       </c>
       <c r="U26" t="n">
         <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -3557,31 +3557,31 @@
         <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB26" t="n">
         <v>2.18</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="AD26" t="n">
         <v>1.45</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>2.03</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.2</v>
+        <v>3.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.09</v>
       </c>
-      <c r="M27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>21</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.53</v>
+        <v>2.18</v>
       </c>
       <c r="AC27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>7.71</v>
+        <v>1.2</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="P28" t="n">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.24</v>
+        <v>4.28</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="T28" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.28</v>
+        <v>3.24</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.38</v>
+        <v>2.64</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -4253,10 +4253,10 @@
         <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
         <v>7.5</v>
@@ -4351,10 +4351,10 @@
         <v>2.34</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
         <v>2.92</v>
@@ -4378,13 +4378,13 @@
         <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W33" t="n">
         <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
         <v>1.27</v>
@@ -4396,7 +4396,7 @@
         <v>2.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC33" t="n">
         <v>3.45</v>
@@ -4411,10 +4411,10 @@
         <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4470,10 +4470,10 @@
         <v>4.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O34" t="n">
         <v>4.45</v>
@@ -4485,7 +4485,7 @@
         <v>2.36</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
         <v>2.77</v>
@@ -4512,13 +4512,13 @@
         <v>3.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
         <v>1.84</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AD34" t="n">
         <v>1.31</v>
@@ -4586,22 +4586,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="R35" t="n">
         <v>1.5</v>
@@ -4610,34 +4610,34 @@
         <v>2.42</v>
       </c>
       <c r="T35" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U35" t="n">
         <v>1.28</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA35" t="n">
         <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.9</v>
+        <v>4.62</v>
       </c>
       <c r="AD35" t="n">
         <v>1.16</v>
@@ -4705,16 +4705,16 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M36" t="n">
         <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="P36" t="n">
         <v>2.55</v>
@@ -4729,7 +4729,7 @@
         <v>2.94</v>
       </c>
       <c r="T36" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U36" t="n">
         <v>1.44</v>
@@ -4738,10 +4738,10 @@
         <v>6.25</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
         <v>1.21</v>
@@ -4756,13 +4756,13 @@
         <v>2.04</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AF36" t="n">
         <v>1.46</v>
@@ -4771,7 +4771,7 @@
         <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.21</v>
+        <v>3.65</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4824,22 +4824,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
         <v>2.45</v>
       </c>
       <c r="O37" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R37" t="n">
         <v>1.45</v>
@@ -4851,13 +4851,13 @@
         <v>3.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="W37" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
         <v>1.05</v>
@@ -4866,31 +4866,31 @@
         <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE37" t="n">
         <v>1.84</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -781,22 +781,22 @@
         <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O3" t="n">
         <v>7.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>2.47</v>
@@ -820,13 +820,13 @@
         <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>3.85</v>
@@ -838,10 +838,10 @@
         <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
         <v>1.05</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
         <v>5.6</v>
@@ -1031,13 +1031,13 @@
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="T5" t="n">
         <v>3.25</v>
@@ -1061,7 +1061,7 @@
         <v>2.63</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
         <v>1.55</v>
@@ -1076,13 +1076,13 @@
         <v>2.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.23</v>
+        <v>2.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45994.5</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="N8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>2.35</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>1.84</v>
       </c>
       <c r="O11" t="n">
-        <v>2.81</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.34</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.87</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>4.56</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>3.16</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>6.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
         <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>6.33</v>
+        <v>2.61</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.47</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
         <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.61</v>
+        <v>6.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.6</v>
+        <v>2.47</v>
       </c>
       <c r="R15" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
         <v>4.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.92</v>
+        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>4.56</v>
+        <v>2.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.16</v>
+        <v>6.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.92</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC17" t="n">
         <v>5.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AF17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.61</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.02</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.96</v>
+        <v>1.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.82</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.39</v>
+        <v>1.53</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.47</v>
+        <v>8.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.63</v>
+        <v>2.09</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>6.15</v>
+        <v>4.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>5.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>4.78</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>3.96</v>
       </c>
       <c r="M19" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>1.82</v>
       </c>
       <c r="O19" t="n">
-        <v>1.53</v>
+        <v>4.39</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.5</v>
+        <v>2.47</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.7</v>
       </c>
-      <c r="V19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AF19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.78</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.32</v>
+        <v>8.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
         <v>6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.63</v>
+        <v>2.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.28</v>
+        <v>4.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>4.18</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
         <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.27</v>
+        <v>3.51</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.88</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>4.18</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.06</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
-        <v>5.75</v>
+        <v>3.96</v>
       </c>
       <c r="N23" t="n">
-        <v>9.35</v>
+        <v>6.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="P23" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.5</v>
+        <v>5.89</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="P24" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.32</v>
+        <v>3.32</v>
       </c>
       <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.09</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>11.5</v>
+        <v>3.29</v>
       </c>
       <c r="N25" t="n">
-        <v>21</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.37</v>
       </c>
-      <c r="P25" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>13.29</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="AH25" t="n">
-        <v>7.71</v>
+        <v>1.52</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="N26" t="n">
-        <v>8.58</v>
+        <v>17</v>
       </c>
       <c r="O26" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="P26" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.43</v>
+        <v>13.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
-        <v>5.3</v>
+        <v>3.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.23</v>
+        <v>7.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.18</v>
+        <v>3.38</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.71</v>
+        <v>1.64</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.66</v>
+        <v>3.39</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.48</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.2</v>
+        <v>3.66</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.66</v>
+        <v>3.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>2.68</v>
+        <v>5.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.28</v>
+        <v>2.15</v>
       </c>
       <c r="R28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.4</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.71</v>
+        <v>1.21</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.65</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.37</v>
-      </c>
       <c r="Q29" t="n">
-        <v>3.24</v>
+        <v>8.41</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
         <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.42</v>
+        <v>1.74</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>3.42</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
         <v>1.8</v>
@@ -4036,16 +4036,16 @@
         <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
         <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
         <v>1.83</v>
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>4.8</v>
@@ -4155,7 +4155,7 @@
         <v>3.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
         <v>1.95</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,43 +4229,43 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="P32" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.78</v>
+        <v>3.64</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
         <v>1.27</v>
@@ -4274,28 +4274,28 @@
         <v>3.18</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,43 +4348,43 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="T33" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V33" t="n">
-        <v>6.95</v>
+        <v>7.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
         <v>1.27</v>
@@ -4393,28 +4393,28 @@
         <v>3.18</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.62</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="O34" t="n">
         <v>4.45</v>
@@ -4512,10 +4512,10 @@
         <v>3.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AC34" t="n">
         <v>3.45</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="O35" t="n">
         <v>3.1</v>
@@ -4631,10 +4631,10 @@
         <v>2.7</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
         <v>4.62</v>
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
         <v>1.67</v>
@@ -4750,10 +4750,10 @@
         <v>3.62</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.04</v>
       </c>
       <c r="AC36" t="n">
         <v>3</v>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
         <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
         <v>3.4</v>
@@ -4869,10 +4869,10 @@
         <v>3.05</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>3.82</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,70 +659,70 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
-        <v>6.68</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
         <v>1.1</v>
@@ -790,13 +790,13 @@
         <v>7.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
         <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
         <v>2.47</v>
@@ -829,7 +829,7 @@
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="AD3" t="n">
         <v>1.21</v>
@@ -841,10 +841,10 @@
         <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>45994.375</v>
@@ -897,25 +897,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="O4" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
         <v>2.47</v>
@@ -924,37 +924,37 @@
         <v>3.05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z4" t="n">
         <v>2.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AF4" t="n">
         <v>1.7</v>
@@ -1025,7 +1025,7 @@
         <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="P5" t="n">
         <v>1.97</v>
@@ -1058,7 +1058,7 @@
         <v>1.39</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AA5" t="n">
         <v>2.3</v>
@@ -1067,7 +1067,7 @@
         <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="AD5" t="n">
         <v>1.15</v>
@@ -1076,13 +1076,13 @@
         <v>2.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
         <v>2.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45994.5</v>
@@ -1138,7 +1138,7 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>3.78</v>
       </c>
       <c r="N6" t="n">
         <v>7</v>
@@ -1150,16 +1150,16 @@
         <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.050000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
         <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
@@ -1174,28 +1174,28 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
         <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
         <v>1.19</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>3.69</v>
       </c>
       <c r="N9" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>7.6</v>
+        <v>6.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="AD10" t="n">
         <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.84</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>7.3</v>
+        <v>12</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>4.56</v>
+        <v>4.43</v>
       </c>
       <c r="P12" t="n">
         <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
         <v>9.199999999999999</v>
@@ -1885,7 +1885,7 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
         <v>1.65</v>
@@ -1894,13 +1894,13 @@
         <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AB12" t="n">
         <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.35</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
         <v>1.07</v>
@@ -1915,7 +1915,7 @@
         <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>1.84</v>
       </c>
       <c r="O13" t="n">
-        <v>2.61</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.6</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.02</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.78</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,37 +2087,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>4.61</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2132,22 +2132,22 @@
         <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>6.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
         <v>1.36</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
-        <v>6.33</v>
+        <v>2.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.47</v>
+        <v>6.41</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.25</v>
       </c>
-      <c r="T15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>2.27</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41</v>
+        <v>2.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.34</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S17" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T17" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V17" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2572,13 +2572,13 @@
         <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
         <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
         <v>1.21</v>
@@ -2587,13 +2587,13 @@
         <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W18" t="n">
         <v>1.15</v>
@@ -2602,10 +2602,10 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.72</v>
+        <v>5.5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.6</v>
@@ -2620,7 +2620,7 @@
         <v>1.57</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>1.74</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M20" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.5</v>
+        <v>2.85</v>
       </c>
       <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.33</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.7</v>
+        <v>3.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.18</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.46</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.08</v>
+        <v>2.79</v>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.89</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="U23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>4.75</v>
+        <v>6.6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.3</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.32</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.26</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3405,19 +3405,19 @@
         <v>2.28</v>
       </c>
       <c r="O25" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
         <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
         <v>2.53</v>
@@ -3426,19 +3426,19 @@
         <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="W25" t="n">
         <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA25" t="n">
         <v>1.7</v>
@@ -3453,16 +3453,16 @@
         <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q26" t="n">
         <v>7.8</v>
       </c>
-      <c r="N26" t="n">
-        <v>17</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>13.85</v>
-      </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="U26" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>3.42</v>
+        <v>5.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AH26" t="n">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N27" t="n">
+        <v>17</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>14</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V27" t="n">
         <v>3.2</v>
       </c>
-      <c r="N27" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V27" t="n">
-        <v>7</v>
-      </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.76</v>
+        <v>3.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.18</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>3.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3762,40 +3762,40 @@
         <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>5.15</v>
+        <v>4.95</v>
       </c>
       <c r="P28" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>5.85</v>
+        <v>5.95</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA28" t="n">
         <v>1.6</v>
@@ -3804,16 +3804,16 @@
         <v>2.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG28" t="n">
         <v>1.23</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>9.1</v>
+        <v>3.39</v>
       </c>
       <c r="O29" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>8.41</v>
+        <v>3.76</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.42</v>
+        <v>1.59</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -4000,40 +4000,40 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="U30" t="n">
         <v>1.6</v>
       </c>
       <c r="V30" t="n">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" t="n">
         <v>1.6</v>
@@ -4051,7 +4051,7 @@
         <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
         <v>1.18</v>
@@ -4119,40 +4119,40 @@
         <v>1.78</v>
       </c>
       <c r="O31" t="n">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R31" t="n">
         <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="U31" t="n">
         <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
         <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AA31" t="n">
         <v>1.85</v>
@@ -4161,16 +4161,16 @@
         <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE31" t="n">
         <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
         <v>1.25</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M32" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="P32" t="n">
         <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4476,34 +4476,34 @@
         <v>2.03</v>
       </c>
       <c r="O34" t="n">
-        <v>4.45</v>
+        <v>5.21</v>
       </c>
       <c r="P34" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
         <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V34" t="n">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="W34" t="n">
         <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
         <v>1.31</v>
@@ -4518,22 +4518,22 @@
         <v>1.74</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
         <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4598,37 +4598,37 @@
         <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="T35" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
         <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
         <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA35" t="n">
         <v>2.3</v>
@@ -4637,22 +4637,22 @@
         <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45994.83333333334</v>
@@ -4714,34 +4714,34 @@
         <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>10.7</v>
+        <v>9.5</v>
       </c>
       <c r="R36" t="n">
         <v>1.35</v>
       </c>
       <c r="S36" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T36" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y36" t="n">
         <v>1.21</v>
@@ -4759,19 +4759,19 @@
         <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE36" t="n">
         <v>2.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AG36" t="n">
         <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.65</v>
+        <v>4.12</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4833,40 +4833,40 @@
         <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="R37" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T37" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V37" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
         <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="AA37" t="n">
         <v>2.1</v>
@@ -4875,16 +4875,16 @@
         <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
         <v>1.36</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>6.51</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="U10" t="n">
         <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.8</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.82</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>8.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="O12" t="n">
-        <v>4.43</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.26</v>
+        <v>2.17</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T12" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>5.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>6.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>3.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.34</v>
+        <v>5.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.46</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
         <v>9.199999999999999</v>
@@ -2123,7 +2123,7 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.65</v>
@@ -2132,13 +2132,13 @@
         <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD14" t="n">
         <v>1.07</v>
@@ -2153,7 +2153,7 @@
         <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>1.84</v>
       </c>
       <c r="O15" t="n">
-        <v>2.27</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.41</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.09</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>5.7</v>
       </c>
       <c r="O16" t="n">
-        <v>9.300000000000001</v>
+        <v>2.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.17</v>
+        <v>6.41</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.01</v>
+        <v>2.09</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>1.83</v>
       </c>
       <c r="O18" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.78</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.96</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.82</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
-        <v>4.39</v>
+        <v>1.57</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.47</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>6.15</v>
+        <v>4.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>4.78</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>2.08</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="T20" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>4.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.48</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.78</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC21" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.96</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.08</v>
+        <v>2.79</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="T22" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>6.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
+        <v>9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.7</v>
       </c>
-      <c r="O24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AG24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH24" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>4.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.84</v>
+        <v>2.61</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M26" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N26" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O26" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>3.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.41</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="V26" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q27" t="n">
         <v>7.8</v>
       </c>
-      <c r="N27" t="n">
-        <v>17</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>14</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O28" t="n">
-        <v>4.95</v>
+        <v>2.9</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.35</v>
+        <v>3.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V28" t="n">
-        <v>5.95</v>
+        <v>7.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.2</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.76</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="T29" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>3.82</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>2.28</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.82</v>
+        <v>1.77</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="T31" t="n">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>3.1</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,49 +4253,49 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
         <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -4372,49 +4372,49 @@
         <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
         <v>3.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>9.5</v>
+        <v>2.95</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="T36" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="V36" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.12</v>
+        <v>1.4</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.95</v>
+        <v>9.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE37" t="n">
         <v>2.53</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.4</v>
+        <v>4.12</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>6.51</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="U10" t="n">
         <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
         <v>9.199999999999999</v>
@@ -1766,7 +1766,7 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
         <v>1.65</v>
@@ -1775,13 +1775,13 @@
         <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
         <v>1.07</v>
@@ -1796,7 +1796,7 @@
         <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>8.5</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.45</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>9.300000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.17</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.55</v>
+        <v>6.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="O13" t="n">
-        <v>6.51</v>
+        <v>2.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>6.41</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.25</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.45</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>8.5</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.45</v>
       </c>
       <c r="O14" t="n">
-        <v>4.43</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.26</v>
+        <v>2.17</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T14" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.95</v>
+        <v>5.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1.84</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="V15" t="n">
-        <v>7.3</v>
+        <v>12</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.41</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AE16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.77</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3.95</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.15</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.06</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.1</v>
+        <v>1.23</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.1</v>
       </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>4.78</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>1.83</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.78</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>4.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>4.75</v>
+        <v>7.7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z21" t="n">
         <v>3.75</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AA21" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
-        <v>2.79</v>
+        <v>1.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>5.7</v>
+        <v>3.96</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="P24" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
         <v>3.24</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O25" t="n">
-        <v>4.95</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.35</v>
+        <v>3.76</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>7.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.07</v>
       </c>
-      <c r="M26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>17</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P26" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>14</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.64</v>
+        <v>2.61</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.95</v>
+        <v>1.21</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>17</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>14</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V28" t="n">
         <v>3.2</v>
       </c>
-      <c r="N28" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.2</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.76</v>
+        <v>3.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.16</v>
+        <v>1.64</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.59</v>
+        <v>3.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>3.82</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.64</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>3.1</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
-        <v>1.77</v>
+        <v>3.82</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>2.28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.42</v>
+        <v>2.71</v>
       </c>
       <c r="U31" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M32" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,49 +4253,49 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
         <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -4372,49 +4372,49 @@
         <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
         <v>3.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.95</v>
+        <v>9.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE36" t="n">
         <v>2.53</v>
       </c>
-      <c r="T36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.4</v>
+        <v>4.12</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>9.5</v>
+        <v>2.95</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="T37" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U37" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.62</v>
+        <v>2.83</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.12</v>
+        <v>1.4</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.9</v>
+        <v>5.68</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -692,7 +692,7 @@
         <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -704,10 +704,10 @@
         <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC2" t="n">
         <v>3.25</v>
@@ -716,10 +716,10 @@
         <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
         <v>1.23</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="O4" t="n">
         <v>5.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -942,10 +942,10 @@
         <v>2.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
         <v>3.72</v>
@@ -957,7 +957,7 @@
         <v>2.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG4" t="n">
         <v>1.29</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.78</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.93</v>
@@ -1165,7 +1165,7 @@
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1177,13 +1177,13 @@
         <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
         <v>3.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="O10" t="n">
-        <v>6.51</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="T10" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AD10" t="n">
         <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.43</v>
+        <v>2.27</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.26</v>
+        <v>6.41</v>
       </c>
       <c r="R11" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>2.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="M12" t="n">
         <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>6.51</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>3.78</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V12" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -1888,34 +1888,34 @@
         <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.15</v>
+        <v>5.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.41</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.07</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AE13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH13" t="n">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.74</v>
+        <v>1.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.55</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.35</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S15" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V16" t="n">
         <v>9.199999999999999</v>
@@ -2361,7 +2361,7 @@
         <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y16" t="n">
         <v>1.65</v>
@@ -2370,13 +2370,13 @@
         <v>2.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD16" t="n">
         <v>1.07</v>
@@ -2391,7 +2391,7 @@
         <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>12</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.7</v>
       </c>
-      <c r="O20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AG20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH20" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG21" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="M22" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.78</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC22" t="n">
-        <v>2.8</v>
+        <v>3.48</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.75</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.2</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.76</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V25" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.16</v>
+        <v>2.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>3.39</v>
       </c>
       <c r="O26" t="n">
-        <v>4.95</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.35</v>
+        <v>3.76</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>5.95</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.61</v>
+        <v>3.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="N27" t="n">
-        <v>9.1</v>
+        <v>17</v>
       </c>
       <c r="O27" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41</v>
+        <v>1.84</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.48</v>
+        <v>2.12</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q28" t="n">
         <v>7.8</v>
       </c>
-      <c r="N28" t="n">
-        <v>17</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>14</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.64</v>
+        <v>2.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>4.95</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.84</v>
+        <v>2.61</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,49 +4253,49 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
         <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -4372,49 +4372,49 @@
         <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
         <v>3.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -659,70 +659,70 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
         <v>1.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
         <v>1.1</v>
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O3" t="n">
         <v>8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7.9</v>
       </c>
       <c r="P3" t="n">
         <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
         <v>3.08</v>
@@ -817,28 +817,28 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB3" t="n">
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
         <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG3" t="n">
         <v>1.18</v>
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O4" t="n">
         <v>5.4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
         <v>2.5</v>
@@ -921,7 +921,7 @@
         <v>2.47</v>
       </c>
       <c r="T4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
         <v>1.35</v>
@@ -939,28 +939,28 @@
         <v>1.43</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE4" t="n">
         <v>2.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
         <v>1.15</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="P5" t="n">
         <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.47</v>
@@ -1055,16 +1055,16 @@
         <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
         <v>2.59</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
         <v>4.25</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.93</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.7</v>
+        <v>5.61</v>
       </c>
       <c r="R6" t="n">
         <v>1.39</v>
@@ -1165,7 +1165,7 @@
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1174,16 +1174,16 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AC6" t="n">
         <v>3.5</v>
@@ -1192,10 +1192,10 @@
         <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
         <v>1.19</v>
@@ -1299,10 +1299,10 @@
         <v>3.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AC7" t="n">
         <v>3.14</v>
@@ -1397,7 +1397,7 @@
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
         <v>1.36</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>9.300000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.17</v>
+        <v>4.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="U10" t="n">
         <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
         <v>5.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>8.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>5.7</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>2.27</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.41</v>
+        <v>2.17</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>5.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.09</v>
+        <v>1.01</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O12" t="n">
-        <v>6.51</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
         <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.45</v>
+        <v>6.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.75</v>
+        <v>6.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4.1</v>
+        <v>4.38</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.34</v>
+        <v>5.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.83</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>6.45</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="T15" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>1.03</v>
@@ -2245,34 +2245,34 @@
         <v>1.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC15" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M16" t="n">
         <v>3.45</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.7</v>
-      </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.43</v>
+        <v>2.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.26</v>
+        <v>6.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.17</v>
       </c>
-      <c r="V16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AE16" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>2.09</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>3.8</v>
+        <v>1.84</v>
       </c>
       <c r="O17" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.33</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3.82</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>12</v>
+        <v>7.3</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2614,10 +2614,10 @@
         <v>2.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -2626,10 +2626,10 @@
         <v>1.74</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="M19" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
         <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
         <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="T19" t="n">
         <v>2.6</v>
@@ -2724,7 +2724,7 @@
         <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="AA19" t="n">
         <v>1.75</v>
@@ -2733,19 +2733,19 @@
         <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
         <v>1.22</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="M20" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.78</v>
+        <v>2.78</v>
       </c>
       <c r="P20" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>6.65</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.6</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="O21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z21" t="n">
         <v>4.5</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
         <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="T22" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V22" t="n">
         <v>7.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>2.79</v>
+        <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="T23" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>3.48</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>3.26</v>
       </c>
       <c r="M24" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.08</v>
+        <v>3.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.31</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.13</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.52</v>
+        <v>3.56</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>4.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>1.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U25" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="M26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O26" t="n">
         <v>3.2</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.9</v>
-      </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>7.2</v>
+        <v>5.95</v>
       </c>
       <c r="W26" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="M27" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>17</v>
+        <v>9.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>6.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="T27" t="n">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH27" t="n">
         <v>3.2</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>3.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>9.1</v>
+        <v>19</v>
       </c>
       <c r="O28" t="n">
-        <v>1.74</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.41</v>
+        <v>1.78</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>3.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.2</v>
+        <v>6.05</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>4.95</v>
+        <v>2.91</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.35</v>
+        <v>3.82</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>7.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3991,19 +3991,19 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>5.46</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O30" t="n">
         <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
         <v>7</v>
@@ -4012,49 +4012,49 @@
         <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V30" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
         <v>4.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC30" t="n">
         <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
         <v>3.1</v>
@@ -4110,34 +4110,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="O31" t="n">
         <v>3.82</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
         <v>2.28</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
         <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
         <v>6.5</v>
@@ -4152,31 +4152,31 @@
         <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE31" t="n">
         <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG31" t="n">
         <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M32" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,49 +4253,49 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -4372,49 +4372,49 @@
         <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V33" t="n">
-        <v>7.6</v>
+        <v>6.95</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.12</v>
+        <v>3.33</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4488,7 +4488,7 @@
         <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
         <v>2.8</v>
@@ -4500,16 +4500,16 @@
         <v>6.85</v>
       </c>
       <c r="W34" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
         <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AA34" t="n">
         <v>1.96</v>
@@ -4521,7 +4521,7 @@
         <v>3.24</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE34" t="n">
         <v>1.84</v>
@@ -4530,10 +4530,10 @@
         <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4598,37 +4598,37 @@
         <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="R35" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T35" t="n">
         <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V35" t="n">
         <v>8.5</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="AA35" t="n">
         <v>2.3</v>
@@ -4640,19 +4640,19 @@
         <v>4.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AF35" t="n">
         <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45994.83333333334</v>
@@ -4714,7 +4714,7 @@
         <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="P36" t="n">
         <v>2.6</v>
@@ -4732,22 +4732,22 @@
         <v>2.59</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
         <v>6</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
         <v>1.21</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="AA36" t="n">
         <v>1.8</v>
@@ -4759,19 +4759,19 @@
         <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4860,10 +4860,10 @@
         <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
         <v>2.83</v>
@@ -4875,7 +4875,7 @@
         <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD37" t="n">
         <v>1.18</v>
@@ -4884,13 +4884,13 @@
         <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG37" t="n">
         <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1263,64 +1263,64 @@
         <v>2.65</v>
       </c>
       <c r="O7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.08</v>
       </c>
-      <c r="P7" t="n">
+      <c r="AA7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45994.5625</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
         <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
         <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
         <v>1.36</v>
@@ -1412,28 +1412,28 @@
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
         <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>3.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
         <v>1.13</v>
@@ -1614,34 +1614,34 @@
         <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
         <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="T10" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="U10" t="n">
         <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
@@ -1650,10 +1650,10 @@
         <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AA10" t="n">
         <v>2.88</v>
@@ -1662,7 +1662,7 @@
         <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="AD10" t="n">
         <v>1.12</v>
@@ -1674,10 +1674,10 @@
         <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8.5</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>9.300000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.17</v>
+        <v>5.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="S11" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T11" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.55</v>
+        <v>6.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="M12" t="n">
         <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
@@ -1864,22 +1864,22 @@
         <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="R12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -1888,13 +1888,13 @@
         <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB12" t="n">
         <v>1.36</v>
@@ -1903,19 +1903,19 @@
         <v>6.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG12" t="n">
         <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>2.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>4.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>3.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AB13" t="n">
         <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.15</v>
+        <v>5.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.43</v>
       </c>
-      <c r="AG13" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>4.38</v>
+        <v>9.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>1.61</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>6.45</v>
+        <v>2.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="T15" t="n">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AC15" t="n">
-        <v>5.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.08</v>
       </c>
-      <c r="AE15" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1.69</v>
       </c>
       <c r="O16" t="n">
-        <v>2.27</v>
+        <v>6.45</v>
       </c>
       <c r="P16" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.1</v>
+        <v>2.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.69</v>
+        <v>2.21</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2444,19 +2444,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="N17" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>5.09</v>
       </c>
       <c r="P17" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="Q17" t="n">
         <v>2.66</v>
@@ -2465,22 +2465,22 @@
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
         <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.28</v>
@@ -2489,28 +2489,28 @@
         <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.23</v>
+        <v>4.16</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>1.77</v>
       </c>
       <c r="O18" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="T18" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="U18" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="V18" t="n">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.16</v>
+        <v>1.23</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.77</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.84</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>4.6</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.16</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>2.16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.96</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.09</v>
+        <v>2.78</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="T21" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>4.75</v>
+        <v>6.65</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>3.64</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.25</v>
+        <v>1.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V22" t="n">
-        <v>7.9</v>
+        <v>4.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.56</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>9.1</v>
       </c>
       <c r="O26" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>6.28</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="U26" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V26" t="n">
-        <v>5.95</v>
+        <v>5.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
         <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.47</v>
+        <v>3.2</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>9.1</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.76</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.2</v>
+        <v>1.59</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="T29" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>7.3</v>
+        <v>5.95</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.34</v>
       </c>
-      <c r="M30" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="N30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>5.46</v>
       </c>
       <c r="N31" t="n">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>3.82</v>
+        <v>1.77</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.11</v>
+        <v>2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="N32" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,49 +4253,49 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>7.6</v>
+        <v>6.95</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
         <v>3.33</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="O33" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="R33" t="n">
         <v>1.4</v>
@@ -4372,49 +4372,49 @@
         <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U33" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V33" t="n">
-        <v>6.95</v>
+        <v>7.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
         <v>3.33</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.25</v>
+        <v>2.95</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
-        <v>9.5</v>
+        <v>2.95</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S36" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="T36" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V36" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.98</v>
+        <v>2.83</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.8</v>
+        <v>1.38</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.95</v>
+        <v>1.25</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.95</v>
+        <v>9.5</v>
       </c>
       <c r="R37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V37" t="n">
+        <v>6</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.4</v>
       </c>
-      <c r="S37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="AE37" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG37" t="n">
         <v>1.01</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.38</v>
+        <v>3.8</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.1</v>
+        <v>9.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.69</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>3.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>4.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.95</v>
+        <v>3.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="V11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AB11" t="n">
         <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.43</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.31</v>
+        <v>5.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="AD12" t="n">
         <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.7</v>
-      </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>1.69</v>
       </c>
       <c r="O13" t="n">
-        <v>4.43</v>
+        <v>6.45</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.26</v>
+        <v>2.46</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="U13" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.29</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.1</v>
+        <v>3.31</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>2.44</v>
+        <v>2.07</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>6.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>1.69</v>
+        <v>2.33</v>
       </c>
       <c r="O16" t="n">
-        <v>6.45</v>
+        <v>5.09</v>
       </c>
       <c r="P16" t="n">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.17</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>3.74</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.21</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.88</v>
+        <v>1.61</v>
       </c>
       <c r="M17" t="n">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>5.09</v>
+        <v>2.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>6.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>2.09</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
         <v>1.57</v>
@@ -2700,55 +2700,55 @@
         <v>9</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="U19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
         <v>4.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.25</v>
+        <v>2.16</v>
       </c>
       <c r="M20" t="n">
-        <v>3.81</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>6.65</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.98</v>
+        <v>3.26</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD21" t="n">
         <v>1.35</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U22" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>4.75</v>
+        <v>5.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.6</v>
+        <v>3.48</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>10</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH23" t="n">
-        <v>3.48</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.26</v>
+        <v>4.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.81</v>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O24" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="T24" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.75</v>
+        <v>2.56</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.33</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.91</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.82</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.59</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.07</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.34</v>
       </c>
-      <c r="P28" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AH28" t="n">
-        <v>6.05</v>
+        <v>1.59</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.56</v>
+        <v>1.07</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>19</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>3.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>12.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="S29" t="n">
-        <v>2.89</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>3.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.54</v>
+        <v>6.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>3.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.93</v>
+        <v>1.71</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.17</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.47</v>
+        <v>6.05</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>5.46</v>
       </c>
       <c r="N30" t="n">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>3.82</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V30" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.11</v>
+        <v>2.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.34</v>
       </c>
-      <c r="M31" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="N31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.4</v>
+        <v>3.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>45994.71875</v>
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.16</v>
+        <v>3.34</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P32" t="n">
         <v>2.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="R32" t="n">
         <v>1.4</v>
@@ -4253,13 +4253,13 @@
         <v>2.73</v>
       </c>
       <c r="T32" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
         <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
         <v>1.04</v>
@@ -4268,16 +4268,16 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
         <v>3.3</v>
@@ -4286,16 +4286,16 @@
         <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF32" t="n">
         <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="M33" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="N33" t="n">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="P33" t="n">
         <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T33" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="U33" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4467,16 +4467,16 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.72</v>
       </c>
       <c r="N34" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="P34" t="n">
         <v>2.28</v>
@@ -4488,7 +4488,7 @@
         <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T34" t="n">
         <v>2.8</v>
@@ -4500,22 +4500,22 @@
         <v>6.85</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
         <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
         <v>3.24</v>
@@ -4530,10 +4530,10 @@
         <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4586,43 +4586,43 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
         <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="R35" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="T35" t="n">
         <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
         <v>1.42</v>
@@ -4631,19 +4631,19 @@
         <v>2.64</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AF35" t="n">
         <v>1.8</v>
@@ -4652,7 +4652,7 @@
         <v>1.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45994.83333333334</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.95</v>
+        <v>1.18</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>5.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="P36" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V36" t="n">
+        <v>6</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB36" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC36" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.38</v>
+        <v>3.7</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.25</v>
+        <v>2.9</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="N37" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>1.67</v>
+        <v>3.7</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>9.5</v>
+        <v>2.95</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="T37" t="n">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V37" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.8</v>
+        <v>1.42</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -1257,70 +1257,70 @@
         <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
         <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="T7" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
         <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>45994.5625</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="O9" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>45994.58333333334</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.2</v>
+        <v>3.17</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="T10" t="n">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
@@ -1650,34 +1650,34 @@
         <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
         <v>2.88</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>4.43</v>
+        <v>9.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.26</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.98</v>
+        <v>3.78</v>
       </c>
       <c r="U11" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC11" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1852,19 +1852,19 @@
         <v>1.83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="P12" t="n">
         <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.95</v>
+        <v>6.29</v>
       </c>
       <c r="R12" t="n">
         <v>1.68</v>
@@ -1885,19 +1885,19 @@
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
         <v>2.97</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
         <v>6.1</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>6.45</v>
+        <v>4.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.46</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="T13" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.35</v>
+        <v>5.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>1.48</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>9.4</v>
+        <v>2.27</v>
       </c>
       <c r="P14" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>6.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
         <v>3.3</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.8</v>
-      </c>
       <c r="N15" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>5.54</v>
       </c>
       <c r="P15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="O16" t="n">
-        <v>5.09</v>
+        <v>2.93</v>
       </c>
       <c r="P16" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.66</v>
+        <v>5.03</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.13</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>5.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.61</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.46</v>
-      </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.16</v>
+        <v>1.19</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.77</v>
+        <v>12</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>9.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="V18" t="n">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.1</v>
       </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>4.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>45994.625</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.18</v>
+        <v>3.95</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>1.68</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.22</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Z19" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>45994.625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.16</v>
+        <v>3.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.78</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="V20" t="n">
-        <v>6.65</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.64</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.55</v>
+        <v>4.25</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.81</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="O21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG21" t="n">
         <v>2.1</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.33</v>
+        <v>2.16</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.79</v>
+        <v>2.78</v>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>5.9</v>
+        <v>6.65</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF22" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG22" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.48</v>
+        <v>1.72</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.26</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.85</v>
+        <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="T23" t="n">
-        <v>3.08</v>
+        <v>2.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.08</v>
+        <v>3.84</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>3.48</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.25</v>
+        <v>1.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.3</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>7.9</v>
+        <v>4.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.1</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.56</v>
+        <v>4.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>5.95</v>
+        <v>6.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.75</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>3.82</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="T27" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U27" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.06</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="O28" t="n">
-        <v>2.91</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.82</v>
+        <v>12.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="S28" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.88</v>
+        <v>1.78</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>7.3</v>
+        <v>3.4</v>
       </c>
       <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.03</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.59</v>
+        <v>6.05</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.07</v>
       </c>
-      <c r="M29" t="n">
-        <v>11</v>
-      </c>
-      <c r="N29" t="n">
-        <v>19</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.95</v>
+        <v>3.54</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.28</v>
+        <v>1.81</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.38</v>
+        <v>1.97</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.71</v>
+        <v>2.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.17</v>
       </c>
-      <c r="AF29" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>6.05</v>
+        <v>1.47</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="M32" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="P32" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.74</v>
+        <v>4.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="M33" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="P33" t="n">
         <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T33" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V33" t="n">
+        <v>7</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG33" t="n">
         <v>1.33</v>
       </c>
-      <c r="V33" t="n">
-        <v>8</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>45994.79166666666</v>
@@ -4467,22 +4467,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="M34" t="n">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O34" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R34" t="n">
         <v>1.39</v>
@@ -4491,13 +4491,13 @@
         <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U34" t="n">
         <v>1.38</v>
       </c>
       <c r="V34" t="n">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="W34" t="n">
         <v>1.04</v>
@@ -4506,13 +4506,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB34" t="n">
         <v>1.86</v>
@@ -4533,7 +4533,7 @@
         <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>45994.8125</v>
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="M35" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
         <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="P35" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="R35" t="n">
         <v>1.5</v>
       </c>
       <c r="S35" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U35" t="n">
         <v>1.3</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35" t="n">
         <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AB35" t="n">
         <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>45994.83333333334</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.18</v>
       </c>
-      <c r="M36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>12</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V36" t="n">
-        <v>6</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE36" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.7</v>
+        <v>1.38</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>45994.89583333334</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.9</v>
+        <v>1.29</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH37" t="n">
         <v>3.7</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>45994.89583333334</v>

--- a/jogos_2025-12-03.xlsx
+++ b/jogos_2025-12-03.xlsx
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8.449999999999999</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>8.35</v>
       </c>
       <c r="P3" t="n">
         <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
         <v>3.08</v>
@@ -820,25 +820,25 @@
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
         <v>1.18</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>5.2</v>
+        <v>10.1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.01</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>45994.5</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="N9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>2.35</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>6.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.17</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="T10" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="U10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="V10" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8.5</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>9.9</v>
+        <v>2.93</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>5.03</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="T11" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AE11" t="n">
-        <v>3.04</v>
+        <v>2.28</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.83</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>4.38</v>
       </c>
       <c r="P12" t="n">
         <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.29</v>
+        <v>3.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="T12" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>45994.60416666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="O13" t="n">
-        <v>4.38</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
         <v>1.77</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>6.29</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="S13" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="T13" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.61</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.17</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>3.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.09</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
-        <v>5.54</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.37</v>
+        <v>3.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>2.92</v>
+        <v>3.96</v>
       </c>
       <c r="U15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.32</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="O16" t="n">
-        <v>2.93</v>
+        <v>5.54</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.03</v>
+        <v>2.37</v>
       </c>
       <c r="R16" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.55</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.59</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>6.45</v>
+        <v>2.27</v>
       </c>
       <c r="P17" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.46</v>
+        <v>6.41</v>
       </c>
       <c r="R17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.61</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>45994.60416666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.26</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>2.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.85</v>
+        <v>5.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="T20" t="n">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="U20" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>6.35</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>3.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>2.28</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>45994.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.81</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>45994.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.16</v>
+        <v>4.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.98</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
-        <v>6.65</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.64</v>
+        <v>3.26</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.72</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>45994.6875</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.24</v>
+        <v>2.93</v>
       </c>
       <c r="T23" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AF23" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.48</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>45994.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC24" t="n">
         <v>2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>45994.6875</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.75</v>
+        <v>1.24</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>9.1</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
@@ -3438,31 +3438,31 @@
         <v>1.19</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
         <v>2.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF25" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.16</v>
+        <v>3.04</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>9.1</v>
+        <v>3.39</v>
       </c>
       <c r="O26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.76</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2</v>
-      </c>
       <c r="AC26" t="n">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="O27" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.82</v>
+        <v>3.14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>7.3</v>
+        <v>6.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3756,19 +3756,19 @@
         <v>1.07</v>
       </c>
       <c r="M28" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="N28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>3.91</v>
+        <v>3.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="R28" t="n">
         <v>1.15</v>
@@ -3777,13 +3777,13 @@
         <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="W28" t="n">
         <v>1.25</v>
@@ -3798,28 +3798,28 @@
         <v>6.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.38</v>
+        <v>3.63</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AD28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AE28" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE28" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG28" t="n">
         <v>1.03</v>
       </c>
       <c r="AH28" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="T29" t="n">
         <v>2.62</v>
@@ -3902,43 +3902,43 @@
         <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>5.95</v>
+        <v>6.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AD29" t="n">
         <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>45994.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>5.46</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="U30" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>45994.71875</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.69</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>3.82</v>
+        <v>1.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB31" t="n">
-        <v